--- a/clase/tabla-stride-clase.xlsx
+++ b/clase/tabla-stride-clase.xlsx
@@ -641,12 +641,12 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>El cliente envía el precio y el plan en el cuerpo de la solicitud y el servidor los acepta sin recalcularlos contra el catálogo, por lo que el monto cobrado puede alterarse.</t>
+          <t>El cliente envía la cantidad y el monto en el cuerpo de la solicitud y el servidor los acepta sin validarlos ni recalcularlos contra el catálogo, por lo que el importe cobrado puede alterarse, incluso con valores negativos.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>El estudiante intercepta la solicitud de compra con las herramientas de desarrollo del navegador y cambia el campo "price" de 120000 a 1 antes de confirmar; el cobro se genera por el valor manipulado.</t>
+          <t>El estudiante envía desde la consola del navegador un PUT al ítem del carrito con {"quantity":-100}; el servidor lo acepta y el total del pedido baja por debajo de su valor real.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Validación de formato del monto en el frontend; el backend confía en el precio recibido. Reproducido en Juice Shop (reto 2 de manipulación de precio).</t>
+          <t>Validación de formato en el frontend; el backend confía en la cantidad y el monto recibidos. Reproducido en Juice Shop (reto "Manipulate Basket": cantidad negativa aceptada por el servidor).</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Recalcular siempre el precio en el servidor a partir del identificador del plan en el catálogo, ignorar cualquier monto enviado por el cliente y firmar la orden antes de enviarla a la pasarela.</t>
+          <t>Recalcular siempre el precio en el servidor a partir del identificador del plan en el catálogo, rechazar cantidades no positivas, ignorar cualquier monto enviado por el cliente y firmar la orden antes de enviarla a la pasarela.</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>El estudiante cambia el identificador en la ruta /api/facturas/482 por /api/facturas/481 y obtiene el nombre, documento y últimos dígitos del medio de pago de otro usuario.</t>
+          <t>El estudiante, con su sesión válida, consulta /rest/basket/1 aunque su carrito es el 7, y el servidor le entrega el recurso de otro usuario (UserId 1) sin verificar la propiedad.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Autenticación por token en todos los endpoints, pero la autorización se resuelve solo por sesión válida y no por propiedad del recurso. Reproducido en Juice Shop (reto 3 de acceso al carrito ajeno).</t>
+          <t>Autenticación por token en todos los endpoints, pero la autorización se resuelve solo por sesión válida y no por propiedad del recurso. Reproducido en Juice Shop (reto "View Basket": lectura del carrito de otro usuario por su identificador).</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
